--- a/LoanOfficer-A/2023/completed/77 bijenti.xlsx
+++ b/LoanOfficer-A/2023/completed/77 bijenti.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
-  <workbookPr filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3000" windowWidth="20640" windowHeight="11760" activeTab="1"/>
   </bookViews>
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'MD20000.15-DEc'!$A$3:$N$32</definedName>
   </definedNames>
-  <calcPr calcId="145621" iterateDelta="1E-4"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
@@ -612,7 +612,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/LoanOfficer-A/2023/completed/77 bijenti.xlsx
+++ b/LoanOfficer-A/2023/completed/77 bijenti.xlsx
@@ -400,7 +400,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -435,7 +435,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
